--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -281,7 +281,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -379,7 +379,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -616,7 +616,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1278,7 +1278,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1829,17 +1829,17 @@
   <dimension ref="A1:AN80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.15234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.44921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.4296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="221.828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="190.17578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1848,26 +1848,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2560,7 +2560,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>260</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -6108,7 +6108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>278</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
@@ -8966,7 +8966,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>340</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>362</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>373</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>383</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>394</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>407</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>416</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>443</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>449</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>464</v>
       </c>
@@ -11044,12 +11044,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN80">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
